--- a/assets/constructions/examples/ctd_tgb_radial.xlsx
+++ b/assets/constructions/examples/ctd_tgb_radial.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QD-LL1E26C21D</t>
+          <t>QD-NR2F33C25A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -607,38 +627,36 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G2" t="n">
-        <v>52</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CoroCut QD -size E (QD-NE-0200-0002-CM)</t>
+          <t>CoroCut QD -size F (QD-NF-0250-0002-CM)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COR_BLADE_H:21R</t>
+          <t>COR_BLADE_H:25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>COR_QD-020</t>
+          <t>COR_QD-025</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L2" t="n">
         <v>50</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -649,16 +667,16 @@
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="W2" t="n">
-        <v>21.4</v>
+        <v>25</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="b">
@@ -669,7 +687,7 @@
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>0.131</v>
+        <v>0.075</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -679,97 +697,87 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WGCBSN32M0860</t>
+          <t>VGWSL 32-3SLC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>WGC</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>WID_WC/G..08</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>WC/G..08</t>
-        </is>
-      </c>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>46</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>WIDIA_BLADE_H:32</t>
+          <t>VARGUS_BLADE_H:32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WIDIA_WGC:08</t>
+          <t>VARGUS_VGD:3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>L</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>150.25</v>
+        <v>120</v>
       </c>
       <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
         <v>8</v>
       </c>
-      <c r="T3" t="n">
-        <v>8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>7</v>
-      </c>
       <c r="W3" t="n">
-        <v>25.05</v>
+        <v>24.8</v>
       </c>
       <c r="X3" t="n">
         <v>2</v>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
@@ -778,39 +786,59 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2020 / WIDIA Токарный каталог</t>
-        </is>
+          <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>40349.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BLST 5-26</t>
+          <t>VGWL26-2S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PALBIT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VG-Cut</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>GCMX-5…</t>
-        </is>
-      </c>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PALB_PTS:26</t>
+          <t>VARGUS_BLADE_H:26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PALB_GCMX:5</t>
+          <t>VARGUS_VGD:2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -836,16 +864,16 @@
         <v>110</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="W4" t="n">
         <v>21.4</v>
@@ -866,14 +894,28 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2022/ palbit основной каталог.pdf</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>280.23</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>25762.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QD-NN1H36C21A</t>
+          <t>QD-LL1H40C25A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -897,7 +939,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -907,7 +949,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COR_BLADE_H:21</t>
+          <t>COR_BLADE_H:25R</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -916,24 +958,24 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
@@ -946,7 +988,7 @@
         <v>3.675</v>
       </c>
       <c r="W5" t="n">
-        <v>21.4</v>
+        <v>25.1</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="b">
@@ -957,7 +999,7 @@
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>0.068</v>
+        <v>0.153</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -967,50 +1009,42 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WGCBSN32M0250</t>
+          <t>BLST 5-32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>WGC</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>WID_WC/G..02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>50</v>
-      </c>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WC/G..02</t>
+          <t>GCMX-5…</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WIDIA_BLADE_H:32</t>
+          <t>PALB_PTS:32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>WIDIA_WGC:02</t>
+          <t>PALB_GCMX:5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1033,31 +1067,31 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>150.25</v>
+        <v>150</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="W6" t="n">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1066,8 +1100,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2020 / WIDIA Токарный каталог</t>
-        </is>
+          <t>2022/ palbit основной каталог.pdf</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>161.91</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>14884.99</v>
       </c>
     </row>
   </sheetData>
